--- a/Sheets/One-Shot Premades/Genio.xlsx
+++ b/Sheets/One-Shot Premades/Genio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse\Sheets\One-Shot Premades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse RPG\Sheets\One-Shot Premades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D63D1A-8C0F-45CB-93FA-2DC07AD23AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB75C5FA-4F17-4919-A2E8-AF9A14B82D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frente" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
   <si>
     <t>Defense Score</t>
   </si>
@@ -246,49 +246,19 @@
     <t>Disparo Elemental (Estándar, Instantáneo)</t>
   </si>
   <si>
-    <t>Dominios de Poder (Permanente)</t>
-  </si>
-  <si>
     <t>Genio - Artillero</t>
   </si>
   <si>
-    <t>+1 Melé  +1 Agilidad</t>
-  </si>
-  <si>
-    <t>Brillante</t>
-  </si>
-  <si>
     <t>Disparo Elemental</t>
   </si>
   <si>
-    <t>Golpe Elemental (Estándar, Instantáneo, 5 Foco)</t>
-  </si>
-  <si>
-    <t>+1 Ego  +1 Vigilancia</t>
-  </si>
-  <si>
     <t>[2 a Elección]</t>
   </si>
   <si>
     <t>Melé</t>
   </si>
   <si>
-    <t>Disminuir Poder (Estándar, Concentración, 5+ Foco)</t>
-  </si>
-  <si>
-    <t>Estimular Poder (Estándar, Concentración, 5+ Foco)</t>
-  </si>
-  <si>
-    <t>Eliges un poder de otro personaje en alcance, y que pertenezca a tu Dominio de Poder. Ataque de Lógica vs Defensa de Lógica. En un éxito, divide el rango, área, y duración del poder a la mitad, quita 1 a los efectos de Multiplicador de Daño o Reducción de Daño, y  no puede tener efectos Fantásticos. Si el poder es de Grado mayor a 1, paga 5 Foco adicional por cada Grado mayor.</t>
-  </si>
-  <si>
-    <t>Eliges un poder de otro personaje en alcance, y que pertenezca a tu Dominio de Poder. Duplica el rango, área, y duración del poder, añade 1 a lo efectos de Multiplicador de Daño o Reducción de Daño, y efectos Fantásticos también ocurren en un éxito. Si el poder es de Grado mayor a 1, paga 5 Foco adicional por cada Grado mayor.</t>
-  </si>
-  <si>
     <t>[1 a Elección, entre Energía, Fuerza y Electricidad]</t>
-  </si>
-  <si>
-    <t>Ataque de Lógica vs Defensa de Agilidad a rango normal. En un éxito, daño normal. Si es Fantástico, doble daño y aplica el efecto de tu Elemento.</t>
   </si>
   <si>
     <t>Conocimiento Mecánico</t>
@@ -316,9 +286,6 @@
       </rPr>
       <t xml:space="preserve"> Precisión</t>
     </r>
-  </si>
-  <si>
-    <t>Ataque de Lógica vs Defensa de Melee a rango normal. En un éxito, daño normal. Si es Fantástico, doble daño y aplica el efecto de tu Elemento.</t>
   </si>
   <si>
     <t>Genio - Científico</t>
@@ -337,6 +304,77 @@
       </rPr>
       <t>[1 a Elección]</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dispositivos: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Poderes que provengan de tecnología o dispositivos electrónicos</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Elementos</t>
+  </si>
+  <si>
+    <t>Resiliencia + 1 x 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foco </t>
+  </si>
+  <si>
+    <t>Vigilancia + 1 x 20</t>
+  </si>
+  <si>
+    <t>Aguante</t>
+  </si>
+  <si>
+    <t>Karma</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Grado</t>
+  </si>
+  <si>
+    <t>Avances</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10 Puntos por Grado</t>
+  </si>
+  <si>
+    <t>+5 Avances</t>
+  </si>
+  <si>
+    <t>Alta Tecnología</t>
+  </si>
+  <si>
+    <t>Dependencia Tecnológica</t>
+  </si>
+  <si>
+    <t>Dominios de Poder</t>
+  </si>
+  <si>
+    <t>+2 Agilidad</t>
+  </si>
+  <si>
+    <t>Cuando haces un chequeo de Lógica, tienes Ventaja. Si utilizas un Talento, convierte a esa Ventaja en un Doble Ventaja.</t>
   </si>
   <si>
     <r>
@@ -371,14 +409,38 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, Manipulación a Distancia</t>
+      <t>, Copiar Poder</t>
     </r>
   </si>
   <si>
-    <t>Manipulación a Distancia (Permanente)</t>
-  </si>
-  <si>
-    <t>Puedes usar tu poderes de Manipulación de Poderes a rango en vez de alcance.</t>
+    <t>Elige un poder de otro personaje en alcance, y que pertenezca a tu Dominio de Poder. Duplica el rango, área, y duración del poder, añade 1 a lo efectos de Multiplicador de Daño o Reducción de Daño, y efectos Fantásticos también ocurren en un éxito. Si el poder es de Grado mayor a 1, paga 5 Foco adicional por cada Grado mayor.</t>
+  </si>
+  <si>
+    <t>Elige un poder de otro personaje en rango, y que pertenezca a tu Dominio de Poder. Puedes usar ese poder como si fuese tuyo. Si el poder es de Grado mayor a 1, paga 5 Foco adicional por cada Grado mayor.</t>
+  </si>
+  <si>
+    <t>Disminuir Poder (Estándar, Concentración, 0+ Foco)</t>
+  </si>
+  <si>
+    <t>Estimular Poder (Estándar, Concentración, 0+ Foco)</t>
+  </si>
+  <si>
+    <t>Protección Elemental (Estándar o Reacción, Instantáneo, 5 Foco)</t>
+  </si>
+  <si>
+    <t>Cuando eres atacado vs tus Defensas Físicas. Crea una barrera con un Limite de Daño igual al doble del Foco gastado. Mientras mantienes Concentración, el daño que recibes es reducido a 0. Este poder termina si recibes daño mayor o igual al Limite de Daño.</t>
+  </si>
+  <si>
+    <t>Ingenioso (Permanente, 5 Foco)</t>
+  </si>
+  <si>
+    <t>Ingenioso</t>
+  </si>
+  <si>
+    <t>Brillante (Permanente)</t>
+  </si>
+  <si>
+    <t>Copiar Poder (Estándar, Concentración, 0+ Foco)</t>
   </si>
   <si>
     <r>
@@ -392,7 +454,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Golpe Elemental</t>
+      <t>Protección Elemental,</t>
     </r>
     <r>
       <rPr>
@@ -403,7 +465,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -417,96 +479,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Dispositivos: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Poderes que provengan de tecnología o dispositivos electrónicos</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Dispositivos Elementales</t>
-  </si>
-  <si>
-    <t>Elementos</t>
-  </si>
-  <si>
-    <t>Cuando haces un cheque de Logica, tienes Ventaja. Si utilizas un Talento, convierte a esa Ventaja en un Doble Ventaja.</t>
-  </si>
-  <si>
-    <t>Resiliencia + 1 x 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foco </t>
-  </si>
-  <si>
-    <t>Vigilancia + 1 x 20</t>
-  </si>
-  <si>
-    <t>Aguante</t>
-  </si>
-  <si>
-    <t>Karma</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Grado</t>
-  </si>
-  <si>
-    <t>Avances</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10 Puntos por Grado</t>
-  </si>
-  <si>
-    <t>Cuando usas un poder que haga un ataque de rango, tienes Ventaja en el ataque.</t>
-  </si>
-  <si>
-    <t>+5 Avances</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dispositivos Elementales: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cuando usas poderes de Control Elemental, puedes usar Lógica en vez de Ego para tiradas de acción.</t>
-    </r>
-  </si>
-  <si>
-    <t>Brillante (Gratis, Instantáneo, 5 Foco)</t>
-  </si>
-  <si>
-    <t>Precisión (Gratis, Instantáneo, 5 Foco)</t>
-  </si>
-  <si>
-    <t>Alta Tecnología</t>
-  </si>
-  <si>
-    <t>Dependencia Tecnológica</t>
+    <t>+1 Lógica  +1 Vigilancia</t>
+  </si>
+  <si>
+    <t>Ataque de Lógica vs Defensa de Agilidad a rango normal. En un éxito, daño normal de Aguante. Si es Fantástico, doble daño y aplica el efecto de tu Elemento.</t>
+  </si>
+  <si>
+    <t>Elige un poder de otro personaje en alcance, y que pertenezca a tu Dominio de Poder. Ataque de Lógica vs Defensa de Ego. En un éxito, divide el rango, área, y duración del poder a la mitad, quita 1 a los efectos de Multiplicador de Daño o Reducción de Daño, y  no puede tener efectos Fantásticos. Si el poder es de Grado mayor a 1, paga 5 Foco adicional por cada Grado mayor.</t>
+  </si>
+  <si>
+    <t>Tienes un +1 a tu Multiplicador de Daño de Logica.</t>
   </si>
 </sst>
 </file>
@@ -734,7 +716,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -1502,11 +1484,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC00000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC00000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC00000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC00000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC00000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC00000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1669,9 +1691,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1689,6 +1708,12 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1818,6 +1843,18 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1884,18 +1921,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1933,6 +1958,9 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2010,9 +2038,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2130,6 +2155,21 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2162,6 +2202,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2567,19 +2625,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="e" vm="1">
+      <c r="A1" s="143" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
       <c r="F1" s="30"/>
       <c r="G1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="86"/>
       <c r="K1" s="48" t="s">
         <v>39</v>
       </c>
@@ -2587,75 +2645,75 @@
       <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="136"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="30"/>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="87"/>
-      <c r="K2" s="177" t="s">
+      <c r="H2" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="90"/>
+      <c r="K2" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="178"/>
-      <c r="M2" s="179"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="183"/>
     </row>
     <row r="3" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="136"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
       <c r="F3" s="30"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="89"/>
-      <c r="K3" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="91"/>
-      <c r="M3" s="92"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="92"/>
+      <c r="K3" s="93" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" s="94"/>
+      <c r="M3" s="95"/>
     </row>
     <row r="4" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="136"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
       <c r="F4" s="30"/>
-      <c r="G4" s="84" t="s">
+      <c r="G4" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="87"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="90"/>
       <c r="K4" s="49" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="L4" s="41"/>
       <c r="M4" s="37"/>
     </row>
     <row r="5" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="188" t="s">
+      <c r="B5" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="188"/>
-      <c r="D5" s="189"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="193"/>
       <c r="E5" s="55"/>
       <c r="F5" s="30"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="89"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="92"/>
       <c r="K5" s="58" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L5" s="41"/>
       <c r="M5" s="37"/>
@@ -2665,21 +2723,21 @@
       <c r="G6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="83"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="95"/>
+      <c r="I6" s="86"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="98"/>
     </row>
     <row r="7" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="135"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="142"/>
       <c r="E7" s="34" t="s">
         <v>42</v>
       </c>
@@ -2687,19 +2745,19 @@
       <c r="G7" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="83"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="92"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="86"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="95"/>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
     </row>
     <row r="8" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="152"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="154"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="160"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="161"/>
       <c r="E8" s="35">
         <v>1</v>
       </c>
@@ -2707,13 +2765,13 @@
       <c r="G8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="83"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="92"/>
+      <c r="I8" s="86"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="95"/>
     </row>
     <row r="9" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
@@ -2722,64 +2780,62 @@
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="92"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="95"/>
     </row>
     <row r="10" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="126" t="s">
+      <c r="A10" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="129" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="30"/>
-      <c r="G10" s="180" t="s">
+      <c r="G10" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="181"/>
-      <c r="I10" s="182"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="98"/>
+      <c r="H10" s="185"/>
+      <c r="I10" s="186"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="101"/>
     </row>
     <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="149" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="150"/>
-      <c r="C11" s="150"/>
-      <c r="D11" s="151"/>
-      <c r="E11" s="127"/>
+      <c r="A11" s="156" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="130"/>
       <c r="F11" s="30"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="107"/>
-      <c r="K11" s="102" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="104"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="110"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="107"/>
     </row>
     <row r="12" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="144" t="str">
+      <c r="A12" s="102"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="151" t="str">
         <f>_xlfn.CONCAT("/",IF(A32=0,20,20 + A32*IF(Modifiers!O5,Modifiers!O5,20)) + Modifiers!N5)</f>
-        <v>/20</v>
-      </c>
-      <c r="D12" s="145"/>
+        <v>/40</v>
+      </c>
+      <c r="D12" s="152"/>
       <c r="E12" s="31"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="110"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="92"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="113"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="95"/>
     </row>
     <row r="13" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="30"/>
@@ -2788,63 +2844,63 @@
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="110"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="92"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="113"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="95"/>
     </row>
     <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="126" t="s">
+      <c r="A14" s="77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="129" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="30"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="110"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="92"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="113"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="95"/>
     </row>
     <row r="15" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="149" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="150"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="127"/>
+      <c r="A15" s="156" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="157"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="130"/>
       <c r="F15" s="30"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="113"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="92"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="116"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="95"/>
     </row>
     <row r="16" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="99"/>
-      <c r="B16" s="100"/>
-      <c r="C16" s="144" t="str">
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="151" t="str">
         <f>_xlfn.CONCAT("/",IF(A34=0,20,20 + A34 * IF(Modifiers!O6,Modifiers!O6,20)) + Modifiers!N6)</f>
         <v>/40</v>
       </c>
-      <c r="D16" s="145"/>
+      <c r="D16" s="152"/>
       <c r="E16" s="31"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="110"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="92"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="113"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="95"/>
     </row>
     <row r="17" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30"/>
@@ -2853,90 +2909,90 @@
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="110"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="92"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="113"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="95"/>
     </row>
     <row r="18" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="126" t="s">
+      <c r="A18" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="78"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="129" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="30"/>
-      <c r="G18" s="193"/>
-      <c r="H18" s="194"/>
-      <c r="I18" s="195"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="92"/>
+      <c r="G18" s="197"/>
+      <c r="H18" s="198"/>
+      <c r="I18" s="199"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="95"/>
     </row>
     <row r="19" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="157" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="158"/>
-      <c r="C19" s="159"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="127"/>
+      <c r="A19" s="136" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="137"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="130"/>
       <c r="F19" s="30"/>
-      <c r="G19" s="190" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="191"/>
-      <c r="I19" s="192"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="92"/>
+      <c r="G19" s="194" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="195"/>
+      <c r="I19" s="196"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="95"/>
     </row>
     <row r="20" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="174" t="s">
+      <c r="A20" s="178" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="175"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="176"/>
+      <c r="B20" s="179"/>
+      <c r="C20" s="179"/>
+      <c r="D20" s="180"/>
       <c r="E20" s="32" t="str">
         <f>_xlfn.CONCAT("+",IF(Modifiers!K6="Edge",_xlfn.CONCAT(A34,"E"),A34))</f>
         <v>+1</v>
       </c>
       <c r="F20" s="30"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="110"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="92"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="113"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="95"/>
     </row>
     <row r="21" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="130" t="s">
+      <c r="A21" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="131"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="132"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="30"/>
-      <c r="G21" s="196"/>
-      <c r="H21" s="197"/>
-      <c r="I21" s="198"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="147"/>
-      <c r="M21" s="148"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="201"/>
+      <c r="I21" s="202"/>
+      <c r="K21" s="153"/>
+      <c r="L21" s="154"/>
+      <c r="M21" s="155"/>
     </row>
     <row r="22" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="130"/>
-      <c r="B22" s="131"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="160"/>
+      <c r="A22" s="133"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="139"/>
       <c r="F22" s="30"/>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
@@ -2945,11 +3001,11 @@
       <c r="N22" s="30"/>
     </row>
     <row r="23" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="155"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="154"/>
+      <c r="A23" s="162"/>
+      <c r="B23" s="163"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="161"/>
       <c r="F23" s="30"/>
       <c r="G23" s="71" t="s">
         <v>18</v>
@@ -2970,11 +3026,11 @@
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="44" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H24" s="45"/>
       <c r="I24" s="39" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="J24" s="39"/>
       <c r="K24" s="39"/>
@@ -2982,13 +3038,13 @@
       <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="161" t="s">
+      <c r="A25" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="162"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="162"/>
-      <c r="E25" s="163"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="166"/>
       <c r="F25" s="30"/>
       <c r="G25" s="46"/>
       <c r="H25" s="47"/>
@@ -2999,15 +3055,15 @@
       <c r="M25" s="37"/>
     </row>
     <row r="26" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121" t="s">
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="124"/>
+      <c r="E26" s="127"/>
       <c r="F26" s="30"/>
       <c r="G26" s="46"/>
       <c r="H26" s="47"/>
@@ -3018,18 +3074,18 @@
       <c r="M26" s="37"/>
     </row>
     <row r="27" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="122"/>
-      <c r="B27" s="123"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="125"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="128"/>
       <c r="F27" s="30"/>
       <c r="G27" s="46" t="s">
         <v>48</v>
       </c>
       <c r="H27" s="47"/>
       <c r="I27" s="41" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J27" s="41"/>
       <c r="K27" s="41"/>
@@ -3037,16 +3093,16 @@
       <c r="M27" s="37"/>
     </row>
     <row r="28" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="114">
+      <c r="A28" s="117">
         <v>0</v>
       </c>
-      <c r="B28" s="115"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="137">
+      <c r="B28" s="118"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="144">
         <f xml:space="preserve"> 10 + A28 + Modifiers!B3</f>
         <v>10</v>
       </c>
-      <c r="E28" s="139"/>
+      <c r="E28" s="146"/>
       <c r="F28" s="30"/>
       <c r="G28" s="46"/>
       <c r="H28" s="47"/>
@@ -3057,13 +3113,13 @@
       <c r="M28" s="37"/>
     </row>
     <row r="29" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="118"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="143"/>
+      <c r="A29" s="120" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="121"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="150"/>
       <c r="F29" s="30"/>
       <c r="G29" s="46"/>
       <c r="H29" s="47"/>
@@ -3074,74 +3130,74 @@
       <c r="M29" s="37"/>
     </row>
     <row r="30" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114">
-        <v>1</v>
-      </c>
-      <c r="B30" s="115"/>
-      <c r="C30" s="116"/>
-      <c r="D30" s="137">
+      <c r="A30" s="117">
+        <v>0</v>
+      </c>
+      <c r="B30" s="118"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="144">
         <f>IF(Modifiers!C4,Modifiers!C4,10 + A30 + Modifiers!B4)</f>
-        <v>11</v>
-      </c>
-      <c r="E30" s="139"/>
+        <v>10</v>
+      </c>
+      <c r="E30" s="146"/>
       <c r="F30" s="30"/>
       <c r="G30" s="46" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H30" s="47"/>
-      <c r="I30" s="140" t="s">
+      <c r="I30" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="J30" s="140"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="141"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="148"/>
     </row>
     <row r="31" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="117" t="s">
+      <c r="A31" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="118"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="143"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="150"/>
       <c r="F31" s="30"/>
       <c r="G31" s="46"/>
       <c r="H31" s="47"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="141"/>
+      <c r="I31" s="147"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="147"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="148"/>
     </row>
     <row r="32" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="114">
-        <v>0</v>
-      </c>
-      <c r="B32" s="115"/>
-      <c r="C32" s="116"/>
-      <c r="D32" s="137">
+      <c r="A32" s="117">
+        <v>1</v>
+      </c>
+      <c r="B32" s="118"/>
+      <c r="C32" s="119"/>
+      <c r="D32" s="144">
         <f xml:space="preserve"> 10 + A32 + Modifiers!B5</f>
-        <v>10</v>
-      </c>
-      <c r="E32" s="139"/>
+        <v>11</v>
+      </c>
+      <c r="E32" s="146"/>
       <c r="F32" s="30"/>
       <c r="G32" s="46"/>
       <c r="H32" s="47"/>
-      <c r="I32" s="140"/>
-      <c r="J32" s="140"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="140"/>
-      <c r="M32" s="141"/>
+      <c r="I32" s="147"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="147"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="148"/>
     </row>
     <row r="33" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="117" t="s">
+      <c r="A33" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="118"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="143"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="150"/>
       <c r="F33" s="30"/>
       <c r="G33" s="46"/>
       <c r="H33" s="47"/>
@@ -3152,16 +3208,16 @@
       <c r="M33" s="37"/>
     </row>
     <row r="34" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="114">
+      <c r="A34" s="117">
         <v>1</v>
       </c>
-      <c r="B34" s="115"/>
-      <c r="C34" s="116"/>
-      <c r="D34" s="137">
+      <c r="B34" s="118"/>
+      <c r="C34" s="119"/>
+      <c r="D34" s="144">
         <f xml:space="preserve"> 10 + A34 + Modifiers!B6</f>
         <v>11</v>
       </c>
-      <c r="E34" s="139"/>
+      <c r="E34" s="146"/>
       <c r="F34" s="30"/>
       <c r="G34" s="46"/>
       <c r="H34" s="47"/>
@@ -3172,13 +3228,13 @@
       <c r="M34" s="37"/>
     </row>
     <row r="35" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="118"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="142"/>
-      <c r="E35" s="143"/>
+      <c r="B35" s="121"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="150"/>
       <c r="F35" s="30"/>
       <c r="G35" s="46"/>
       <c r="H35" s="47"/>
@@ -3189,16 +3245,16 @@
       <c r="M35" s="37"/>
     </row>
     <row r="36" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="114">
+      <c r="A36" s="117">
         <v>1</v>
       </c>
-      <c r="B36" s="115"/>
-      <c r="C36" s="116"/>
-      <c r="D36" s="137">
+      <c r="B36" s="118"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="144">
         <f xml:space="preserve"> 10 + A36 + Modifiers!B7</f>
         <v>11</v>
       </c>
-      <c r="E36" s="139"/>
+      <c r="E36" s="146"/>
       <c r="F36" s="30"/>
       <c r="G36" s="46"/>
       <c r="H36" s="47"/>
@@ -3209,13 +3265,13 @@
       <c r="M36" s="37"/>
     </row>
     <row r="37" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="117" t="s">
+      <c r="A37" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="118"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="142"/>
-      <c r="E37" s="143"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="149"/>
+      <c r="E37" s="150"/>
       <c r="F37" s="30"/>
       <c r="G37" s="46"/>
       <c r="H37" s="47"/>
@@ -3226,16 +3282,16 @@
       <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="137">
+      <c r="A38" s="144">
         <v>3</v>
       </c>
-      <c r="B38" s="138"/>
-      <c r="C38" s="139"/>
-      <c r="D38" s="137">
+      <c r="B38" s="145"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="144">
         <f xml:space="preserve"> 10 + A38 + Modifiers!B8</f>
         <v>13</v>
       </c>
-      <c r="E38" s="139"/>
+      <c r="E38" s="146"/>
       <c r="F38" s="30"/>
       <c r="G38" s="46"/>
       <c r="H38" s="47"/>
@@ -3246,13 +3302,13 @@
       <c r="M38" s="37"/>
     </row>
     <row r="39" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="117" t="s">
+      <c r="A39" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="118"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="142"/>
-      <c r="E39" s="143"/>
+      <c r="B39" s="121"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="149"/>
+      <c r="E39" s="150"/>
       <c r="F39" s="30"/>
       <c r="G39" s="46"/>
       <c r="H39" s="47"/>
@@ -3269,22 +3325,22 @@
       <c r="D40" s="30"/>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
-      <c r="G40" s="185"/>
-      <c r="H40" s="186"/>
-      <c r="I40" s="186"/>
-      <c r="J40" s="186"/>
-      <c r="K40" s="186"/>
-      <c r="L40" s="186"/>
-      <c r="M40" s="187"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="190"/>
+      <c r="K40" s="190"/>
+      <c r="L40" s="190"/>
+      <c r="M40" s="191"/>
     </row>
     <row r="41" spans="1:14" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="169" t="s">
+      <c r="A41" s="172" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="170"/>
-      <c r="C41" s="170"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="171"/>
+      <c r="B41" s="173"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="174"/>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
       <c r="H41" s="30"/>
@@ -3295,20 +3351,20 @@
       <c r="M41" s="30"/>
     </row>
     <row r="42" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="172" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="101" t="e" vm="2">
+      <c r="A42" s="175" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="104" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C42" s="168" t="str">
+      <c r="C42" s="171" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G3,Modifiers!G3,$E$8 + Modifiers!F3))</f>
         <v>X 1</v>
       </c>
-      <c r="D42" s="173" t="s">
+      <c r="D42" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="166">
+      <c r="E42" s="169">
         <f>A28</f>
         <v>0</v>
       </c>
@@ -3324,11 +3380,11 @@
       <c r="M42" s="30"/>
     </row>
     <row r="43" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="172"/>
-      <c r="B43" s="101"/>
-      <c r="C43" s="168"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="166"/>
+      <c r="A43" s="175"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="171"/>
+      <c r="D43" s="167"/>
+      <c r="E43" s="169"/>
       <c r="F43" s="30"/>
       <c r="G43" s="50"/>
       <c r="H43" s="51"/>
@@ -3339,22 +3395,22 @@
       <c r="M43" s="52"/>
     </row>
     <row r="44" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="101" t="e" vm="2">
+      <c r="B44" s="104" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C44" s="168" t="str">
+      <c r="C44" s="171" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G5,Modifiers!G5,$E$8 + Modifiers!F5))</f>
         <v>X 1</v>
       </c>
-      <c r="D44" s="164" t="s">
+      <c r="D44" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="166">
+      <c r="E44" s="169">
         <f>A30</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="38"/>
@@ -3366,11 +3422,11 @@
       <c r="M44" s="53"/>
     </row>
     <row r="45" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="172"/>
-      <c r="B45" s="101"/>
-      <c r="C45" s="168"/>
-      <c r="D45" s="164"/>
-      <c r="E45" s="166"/>
+      <c r="A45" s="175"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="171"/>
+      <c r="D45" s="167"/>
+      <c r="E45" s="169"/>
       <c r="F45" s="30"/>
       <c r="G45" s="38"/>
       <c r="H45" s="36"/>
@@ -3382,20 +3438,20 @@
       <c r="N45" s="30"/>
     </row>
     <row r="46" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="172" t="s">
+      <c r="A46" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="101" t="e" vm="2">
+      <c r="B46" s="104" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C46" s="168" t="str">
+      <c r="C46" s="171" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G7,Modifiers!G7,$E$8 + Modifiers!F7))</f>
         <v>X 1</v>
       </c>
-      <c r="D46" s="164" t="s">
+      <c r="D46" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="166">
+      <c r="E46" s="169">
         <f>A36</f>
         <v>1</v>
       </c>
@@ -3410,61 +3466,61 @@
       <c r="N46" s="30"/>
     </row>
     <row r="47" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="172"/>
-      <c r="B47" s="101"/>
-      <c r="C47" s="168"/>
-      <c r="D47" s="164"/>
-      <c r="E47" s="166"/>
+      <c r="A47" s="175"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="171"/>
+      <c r="D47" s="167"/>
+      <c r="E47" s="169"/>
       <c r="F47" s="30"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="109"/>
-      <c r="I47" s="109"/>
-      <c r="J47" s="109"/>
-      <c r="K47" s="109"/>
-      <c r="L47" s="109"/>
-      <c r="M47" s="110"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="112"/>
+      <c r="I47" s="112"/>
+      <c r="J47" s="112"/>
+      <c r="K47" s="112"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="113"/>
     </row>
     <row r="48" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="172" t="s">
+      <c r="A48" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="101" t="e" vm="2">
+      <c r="B48" s="104" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C48" s="168" t="str">
+      <c r="C48" s="171" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G9,Modifiers!G9,$E$8 + Modifiers!F8))</f>
         <v>X 1</v>
       </c>
-      <c r="D48" s="164" t="s">
+      <c r="D48" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="166">
+      <c r="E48" s="169">
         <f>A38</f>
         <v>3</v>
       </c>
       <c r="F48" s="30"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="109"/>
-      <c r="I48" s="109"/>
-      <c r="J48" s="109"/>
-      <c r="K48" s="109"/>
-      <c r="L48" s="109"/>
-      <c r="M48" s="110"/>
+      <c r="G48" s="111"/>
+      <c r="H48" s="112"/>
+      <c r="I48" s="112"/>
+      <c r="J48" s="112"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="112"/>
+      <c r="M48" s="113"/>
     </row>
     <row r="49" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="200"/>
-      <c r="B49" s="199"/>
-      <c r="C49" s="201"/>
-      <c r="D49" s="165"/>
-      <c r="E49" s="167"/>
+      <c r="A49" s="204"/>
+      <c r="B49" s="203"/>
+      <c r="C49" s="177"/>
+      <c r="D49" s="168"/>
+      <c r="E49" s="170"/>
       <c r="F49" s="30"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="109"/>
-      <c r="I49" s="109"/>
-      <c r="J49" s="109"/>
-      <c r="K49" s="109"/>
-      <c r="L49" s="109"/>
-      <c r="M49" s="110"/>
+      <c r="G49" s="111"/>
+      <c r="H49" s="112"/>
+      <c r="I49" s="112"/>
+      <c r="J49" s="112"/>
+      <c r="K49" s="112"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="113"/>
     </row>
     <row r="50" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
@@ -3482,13 +3538,13 @@
       <c r="M50" s="37"/>
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" s="79"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="79"/>
-      <c r="E51" s="80"/>
+      <c r="A51" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="78"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="79"/>
       <c r="F51" s="30"/>
       <c r="G51" s="46"/>
       <c r="H51" s="47"/>
@@ -3499,13 +3555,13 @@
       <c r="M51" s="37"/>
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="149" t="s">
-        <v>89</v>
-      </c>
-      <c r="B52" s="150"/>
-      <c r="C52" s="150"/>
-      <c r="D52" s="150"/>
-      <c r="E52" s="151"/>
+      <c r="A52" s="156" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="157"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="158"/>
       <c r="F52" s="30"/>
       <c r="G52" s="46"/>
       <c r="H52" s="47"/>
@@ -3516,23 +3572,23 @@
       <c r="M52" s="37"/>
     </row>
     <row r="53" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="183"/>
-      <c r="B53" s="184"/>
-      <c r="C53" s="144" t="s">
+      <c r="A53" s="187"/>
+      <c r="B53" s="188"/>
+      <c r="C53" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="D53" s="145"/>
+      <c r="D53" s="152"/>
       <c r="E53" s="54">
         <v>10</v>
       </c>
       <c r="F53" s="30"/>
-      <c r="G53" s="185"/>
-      <c r="H53" s="186"/>
-      <c r="I53" s="186"/>
-      <c r="J53" s="186"/>
-      <c r="K53" s="186"/>
-      <c r="L53" s="186"/>
-      <c r="M53" s="187"/>
+      <c r="G53" s="189"/>
+      <c r="H53" s="190"/>
+      <c r="I53" s="190"/>
+      <c r="J53" s="190"/>
+      <c r="K53" s="190"/>
+      <c r="L53" s="190"/>
+      <c r="M53" s="191"/>
     </row>
     <row r="54" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F54" s="30"/>
@@ -3664,121 +3720,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="229" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="228"/>
+      <c r="B1" s="230"/>
+      <c r="C1" s="230"/>
+      <c r="D1" s="231"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="232" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="234"/>
+      <c r="A2" s="235"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="235"/>
-      <c r="B3" s="236"/>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="236"/>
-      <c r="I3" s="237"/>
+      <c r="A3" s="238"/>
+      <c r="B3" s="239"/>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="239"/>
+      <c r="I3" s="240"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="229"/>
-      <c r="B4" s="230"/>
-      <c r="C4" s="230"/>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="231"/>
+      <c r="A4" s="232"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="234"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="229"/>
-      <c r="B5" s="230"/>
-      <c r="C5" s="230"/>
-      <c r="D5" s="230"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="231"/>
+      <c r="A5" s="232"/>
+      <c r="B5" s="233"/>
+      <c r="C5" s="233"/>
+      <c r="D5" s="233"/>
+      <c r="E5" s="233"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="233"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="234"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="229"/>
-      <c r="B6" s="230"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="230"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="230"/>
-      <c r="I6" s="231"/>
+      <c r="A6" s="232"/>
+      <c r="B6" s="233"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+      <c r="I6" s="234"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="202"/>
-      <c r="B7" s="203"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="204"/>
+      <c r="A7" s="205"/>
+      <c r="B7" s="206"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="207"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="208" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="209"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="210"/>
+      <c r="A8" s="211" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="212"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="212"/>
+      <c r="E8" s="212"/>
+      <c r="F8" s="212"/>
+      <c r="G8" s="212"/>
+      <c r="H8" s="212"/>
+      <c r="I8" s="213"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="211" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="212"/>
-      <c r="I9" s="213"/>
+      <c r="A9" s="214" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="215"/>
+      <c r="C9" s="215"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="215"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="216"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="214"/>
-      <c r="B10" s="215"/>
-      <c r="C10" s="215"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="215"/>
-      <c r="H10" s="215"/>
-      <c r="I10" s="216"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="218"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="218"/>
+      <c r="H10" s="218"/>
+      <c r="I10" s="219"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B11" s="65"/>
       <c r="C11" s="65"/>
@@ -3790,8 +3844,8 @@
       <c r="I11" s="63"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
-        <v>64</v>
+      <c r="A12" s="76" t="s">
+        <v>55</v>
       </c>
       <c r="B12" s="70"/>
       <c r="C12" s="70"/>
@@ -3814,45 +3868,45 @@
       <c r="I13" s="69"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="211" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-      <c r="F14" s="209"/>
-      <c r="G14" s="209"/>
-      <c r="H14" s="209"/>
-      <c r="I14" s="210"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="212"/>
+      <c r="G14" s="212"/>
+      <c r="H14" s="212"/>
+      <c r="I14" s="213"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="211" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-      <c r="F15" s="212"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="212"/>
-      <c r="I15" s="213"/>
+      <c r="A15" s="214" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="215"/>
+      <c r="C15" s="215"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="215"/>
+      <c r="G15" s="215"/>
+      <c r="H15" s="215"/>
+      <c r="I15" s="216"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="214"/>
-      <c r="B16" s="215"/>
-      <c r="C16" s="215"/>
-      <c r="D16" s="215"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="215"/>
-      <c r="G16" s="215"/>
-      <c r="H16" s="215"/>
-      <c r="I16" s="216"/>
+      <c r="A16" s="217"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="218"/>
+      <c r="G16" s="218"/>
+      <c r="H16" s="218"/>
+      <c r="I16" s="219"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B17" s="65"/>
       <c r="C17" s="65"/>
@@ -3864,8 +3918,8 @@
       <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="76" t="s">
-        <v>78</v>
+      <c r="A18" s="75" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="68"/>
       <c r="C18" s="68"/>
@@ -3878,7 +3932,7 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B19" s="65"/>
       <c r="C19" s="65"/>
@@ -3890,54 +3944,54 @@
       <c r="I19" s="63"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="205" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="206"/>
-      <c r="C20" s="206"/>
-      <c r="D20" s="206"/>
-      <c r="E20" s="206"/>
-      <c r="F20" s="206"/>
-      <c r="G20" s="206"/>
-      <c r="H20" s="206"/>
-      <c r="I20" s="207"/>
+      <c r="A20" s="208" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="209"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="209"/>
+      <c r="E20" s="209"/>
+      <c r="F20" s="209"/>
+      <c r="G20" s="209"/>
+      <c r="H20" s="209"/>
+      <c r="I20" s="210"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="205"/>
-      <c r="B21" s="206"/>
-      <c r="C21" s="206"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="206"/>
-      <c r="F21" s="206"/>
-      <c r="G21" s="206"/>
-      <c r="H21" s="206"/>
-      <c r="I21" s="207"/>
+      <c r="A21" s="208"/>
+      <c r="B21" s="209"/>
+      <c r="C21" s="209"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="209"/>
+      <c r="F21" s="209"/>
+      <c r="G21" s="209"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="210"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="205"/>
-      <c r="B22" s="206"/>
-      <c r="C22" s="206"/>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="206"/>
-      <c r="H22" s="206"/>
-      <c r="I22" s="207"/>
+      <c r="A22" s="208"/>
+      <c r="B22" s="209"/>
+      <c r="C22" s="209"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="209"/>
+      <c r="F22" s="209"/>
+      <c r="G22" s="209"/>
+      <c r="H22" s="209"/>
+      <c r="I22" s="210"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
-      <c r="B23" s="218"/>
-      <c r="C23" s="218"/>
-      <c r="D23" s="218"/>
-      <c r="E23" s="218"/>
-      <c r="F23" s="218"/>
-      <c r="G23" s="218"/>
-      <c r="H23" s="218"/>
-      <c r="I23" s="219"/>
+      <c r="A23" s="220"/>
+      <c r="B23" s="221"/>
+      <c r="C23" s="221"/>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="221"/>
+      <c r="G23" s="221"/>
+      <c r="H23" s="221"/>
+      <c r="I23" s="222"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B24" s="65"/>
       <c r="C24" s="65"/>
@@ -3949,249 +4003,249 @@
       <c r="I24" s="63"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="205" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="206"/>
-      <c r="C25" s="206"/>
-      <c r="D25" s="206"/>
-      <c r="E25" s="206"/>
-      <c r="F25" s="206"/>
-      <c r="G25" s="206"/>
-      <c r="H25" s="206"/>
-      <c r="I25" s="207"/>
+      <c r="A25" s="208" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="209"/>
+      <c r="C25" s="209"/>
+      <c r="D25" s="209"/>
+      <c r="E25" s="209"/>
+      <c r="F25" s="209"/>
+      <c r="G25" s="209"/>
+      <c r="H25" s="209"/>
+      <c r="I25" s="210"/>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="205"/>
-      <c r="B26" s="206"/>
-      <c r="C26" s="206"/>
-      <c r="D26" s="206"/>
-      <c r="E26" s="206"/>
-      <c r="F26" s="206"/>
-      <c r="G26" s="206"/>
-      <c r="H26" s="206"/>
-      <c r="I26" s="207"/>
+      <c r="A26" s="208"/>
+      <c r="B26" s="209"/>
+      <c r="C26" s="209"/>
+      <c r="D26" s="209"/>
+      <c r="E26" s="209"/>
+      <c r="F26" s="209"/>
+      <c r="G26" s="209"/>
+      <c r="H26" s="209"/>
+      <c r="I26" s="210"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="205"/>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="206"/>
-      <c r="I27" s="207"/>
+      <c r="A27" s="208"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="209"/>
+      <c r="F27" s="209"/>
+      <c r="G27" s="209"/>
+      <c r="H27" s="209"/>
+      <c r="I27" s="210"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="205"/>
-      <c r="B28" s="206"/>
-      <c r="C28" s="206"/>
-      <c r="D28" s="206"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="206"/>
-      <c r="G28" s="206"/>
-      <c r="H28" s="206"/>
-      <c r="I28" s="207"/>
+      <c r="A28" s="208"/>
+      <c r="B28" s="209"/>
+      <c r="C28" s="209"/>
+      <c r="D28" s="209"/>
+      <c r="E28" s="209"/>
+      <c r="F28" s="209"/>
+      <c r="G28" s="209"/>
+      <c r="H28" s="209"/>
+      <c r="I28" s="210"/>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="220"/>
-      <c r="B29" s="221"/>
-      <c r="C29" s="221"/>
-      <c r="D29" s="221"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="221"/>
-      <c r="H29" s="221"/>
-      <c r="I29" s="222"/>
+      <c r="A29" s="223"/>
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
+      <c r="H29" s="224"/>
+      <c r="I29" s="225"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="220"/>
-      <c r="B30" s="221"/>
-      <c r="C30" s="221"/>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="221"/>
-      <c r="H30" s="221"/>
-      <c r="I30" s="222"/>
+      <c r="A30" s="223"/>
+      <c r="B30" s="224"/>
+      <c r="C30" s="224"/>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="224"/>
+      <c r="H30" s="224"/>
+      <c r="I30" s="225"/>
       <c r="L30" s="72"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="220"/>
-      <c r="B31" s="221"/>
-      <c r="C31" s="221"/>
-      <c r="D31" s="221"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="221"/>
-      <c r="G31" s="221"/>
-      <c r="H31" s="221"/>
-      <c r="I31" s="222"/>
+      <c r="A31" s="223"/>
+      <c r="B31" s="224"/>
+      <c r="C31" s="224"/>
+      <c r="D31" s="224"/>
+      <c r="E31" s="224"/>
+      <c r="F31" s="224"/>
+      <c r="G31" s="224"/>
+      <c r="H31" s="224"/>
+      <c r="I31" s="225"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="220"/>
-      <c r="B32" s="221"/>
-      <c r="C32" s="221"/>
-      <c r="D32" s="221"/>
-      <c r="E32" s="221"/>
-      <c r="F32" s="221"/>
-      <c r="G32" s="221"/>
-      <c r="H32" s="221"/>
-      <c r="I32" s="222"/>
+      <c r="A32" s="223"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="225"/>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="220"/>
-      <c r="B33" s="221"/>
-      <c r="C33" s="221"/>
-      <c r="D33" s="221"/>
-      <c r="E33" s="221"/>
-      <c r="F33" s="221"/>
-      <c r="G33" s="221"/>
-      <c r="H33" s="221"/>
-      <c r="I33" s="222"/>
+      <c r="A33" s="223"/>
+      <c r="B33" s="224"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="225"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="220"/>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="221"/>
-      <c r="I34" s="222"/>
+      <c r="A34" s="223"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="225"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="220"/>
-      <c r="B35" s="221"/>
-      <c r="C35" s="221"/>
-      <c r="D35" s="221"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="221"/>
-      <c r="H35" s="221"/>
-      <c r="I35" s="222"/>
+      <c r="A35" s="223"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="225"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="220"/>
-      <c r="B36" s="221"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="221"/>
-      <c r="E36" s="221"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="221"/>
-      <c r="H36" s="221"/>
-      <c r="I36" s="222"/>
+      <c r="A36" s="223"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="225"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="220"/>
-      <c r="B37" s="221"/>
-      <c r="C37" s="221"/>
-      <c r="D37" s="221"/>
-      <c r="E37" s="221"/>
-      <c r="F37" s="221"/>
-      <c r="G37" s="221"/>
-      <c r="H37" s="221"/>
-      <c r="I37" s="222"/>
+      <c r="A37" s="223"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="224"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="225"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="220"/>
-      <c r="B38" s="221"/>
-      <c r="C38" s="221"/>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="221"/>
-      <c r="H38" s="221"/>
-      <c r="I38" s="222"/>
+      <c r="A38" s="223"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
+      <c r="H38" s="224"/>
+      <c r="I38" s="225"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="220"/>
-      <c r="B39" s="221"/>
-      <c r="C39" s="221"/>
-      <c r="D39" s="221"/>
-      <c r="E39" s="221"/>
-      <c r="F39" s="221"/>
-      <c r="G39" s="221"/>
-      <c r="H39" s="221"/>
-      <c r="I39" s="222"/>
+      <c r="A39" s="223"/>
+      <c r="B39" s="224"/>
+      <c r="C39" s="224"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="224"/>
+      <c r="F39" s="224"/>
+      <c r="G39" s="224"/>
+      <c r="H39" s="224"/>
+      <c r="I39" s="225"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="220"/>
-      <c r="B40" s="221"/>
-      <c r="C40" s="221"/>
-      <c r="D40" s="221"/>
-      <c r="E40" s="221"/>
-      <c r="F40" s="221"/>
-      <c r="G40" s="221"/>
-      <c r="H40" s="221"/>
-      <c r="I40" s="222"/>
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="224"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="224"/>
+      <c r="F40" s="224"/>
+      <c r="G40" s="224"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="225"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="220"/>
-      <c r="B41" s="221"/>
-      <c r="C41" s="221"/>
-      <c r="D41" s="221"/>
-      <c r="E41" s="221"/>
-      <c r="F41" s="221"/>
-      <c r="G41" s="221"/>
-      <c r="H41" s="221"/>
-      <c r="I41" s="222"/>
+      <c r="A41" s="223"/>
+      <c r="B41" s="224"/>
+      <c r="C41" s="224"/>
+      <c r="D41" s="224"/>
+      <c r="E41" s="224"/>
+      <c r="F41" s="224"/>
+      <c r="G41" s="224"/>
+      <c r="H41" s="224"/>
+      <c r="I41" s="225"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="220"/>
-      <c r="B42" s="221"/>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="221"/>
-      <c r="I42" s="222"/>
+      <c r="A42" s="223"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="225"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="220"/>
-      <c r="B43" s="221"/>
-      <c r="C43" s="221"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="221"/>
-      <c r="F43" s="221"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="221"/>
-      <c r="I43" s="222"/>
+      <c r="A43" s="223"/>
+      <c r="B43" s="224"/>
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="225"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="220"/>
-      <c r="B44" s="221"/>
-      <c r="C44" s="221"/>
-      <c r="D44" s="221"/>
-      <c r="E44" s="221"/>
-      <c r="F44" s="221"/>
-      <c r="G44" s="221"/>
-      <c r="H44" s="221"/>
-      <c r="I44" s="222"/>
+      <c r="A44" s="223"/>
+      <c r="B44" s="224"/>
+      <c r="C44" s="224"/>
+      <c r="D44" s="224"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="224"/>
+      <c r="G44" s="224"/>
+      <c r="H44" s="224"/>
+      <c r="I44" s="225"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="220"/>
-      <c r="B45" s="221"/>
-      <c r="C45" s="221"/>
-      <c r="D45" s="221"/>
-      <c r="E45" s="221"/>
-      <c r="F45" s="221"/>
-      <c r="G45" s="221"/>
-      <c r="H45" s="221"/>
-      <c r="I45" s="222"/>
+      <c r="A45" s="223"/>
+      <c r="B45" s="224"/>
+      <c r="C45" s="224"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="224"/>
+      <c r="F45" s="224"/>
+      <c r="G45" s="224"/>
+      <c r="H45" s="224"/>
+      <c r="I45" s="225"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="223"/>
-      <c r="B46" s="224"/>
-      <c r="C46" s="224"/>
-      <c r="D46" s="224"/>
-      <c r="E46" s="224"/>
-      <c r="F46" s="224"/>
-      <c r="G46" s="224"/>
-      <c r="H46" s="224"/>
-      <c r="I46" s="225"/>
+      <c r="A46" s="226"/>
+      <c r="B46" s="227"/>
+      <c r="C46" s="227"/>
+      <c r="D46" s="227"/>
+      <c r="E46" s="227"/>
+      <c r="F46" s="227"/>
+      <c r="G46" s="227"/>
+      <c r="H46" s="227"/>
+      <c r="I46" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -4233,66 +4287,66 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F52ED7-B55C-4544-B1B9-4049608F227A}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="241" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="250" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="251"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="244" t="s">
+    <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="249" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="250"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="258" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="259"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="252" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="245"/>
-      <c r="C2" s="245"/>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="245"/>
-      <c r="I2" s="246"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="247" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="249"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="208" t="s">
+      <c r="B2" s="253"/>
+      <c r="C2" s="253"/>
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="254"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="255" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="256"/>
+      <c r="C3" s="256"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="256"/>
+      <c r="I3" s="257"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="211" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="209"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="210"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="213"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B5" s="73"/>
       <c r="C5" s="73"/>
@@ -4303,221 +4357,253 @@
       <c r="H5" s="73"/>
       <c r="I5" s="60"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="60"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="208" t="s">
+    <row r="6" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="82" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="84"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="244" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="246"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="247" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="209"/>
-      <c r="C7" s="209"/>
-      <c r="D7" s="209"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="210"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="214" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="215"/>
-      <c r="C8" s="215"/>
-      <c r="D8" s="215"/>
-      <c r="E8" s="215"/>
-      <c r="F8" s="215"/>
-      <c r="G8" s="215"/>
-      <c r="H8" s="215"/>
-      <c r="I8" s="216"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="218"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="218"/>
+      <c r="H8" s="218"/>
+      <c r="I8" s="248"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="B9" s="65"/>
       <c r="C9" s="65"/>
       <c r="D9" s="65"/>
-      <c r="E9" s="74"/>
+      <c r="E9" s="81"/>
       <c r="F9" s="65"/>
       <c r="G9" s="65"/>
       <c r="H9" s="65"/>
       <c r="I9" s="63"/>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="205" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="206"/>
-      <c r="C10" s="206"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="206"/>
-      <c r="G10" s="206"/>
-      <c r="H10" s="206"/>
-      <c r="I10" s="207"/>
-      <c r="K10" s="72"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="238"/>
-      <c r="B11" s="239"/>
-      <c r="C11" s="239"/>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="240"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="241" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="242"/>
-      <c r="C13" s="242"/>
-      <c r="D13" s="243"/>
-      <c r="E13" s="250" t="s">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="260" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="261"/>
+      <c r="C10" s="261"/>
+      <c r="D10" s="261"/>
+      <c r="E10" s="261"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
+      <c r="H10" s="261"/>
+      <c r="I10" s="262"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="260"/>
+      <c r="B11" s="261"/>
+      <c r="C11" s="261"/>
+      <c r="D11" s="261"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="261"/>
+      <c r="H11" s="261"/>
+      <c r="I11" s="262"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="263"/>
+      <c r="B12" s="264"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="264"/>
+      <c r="E12" s="264"/>
+      <c r="F12" s="264"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="264"/>
+      <c r="I12" s="265"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="249" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="250"/>
+      <c r="C18" s="250"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="258" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="259"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="252" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="253"/>
+      <c r="C19" s="253"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="253"/>
+      <c r="I19" s="254"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="255" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="251"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="245"/>
-      <c r="C14" s="245"/>
-      <c r="D14" s="245"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="245"/>
-      <c r="G14" s="245"/>
-      <c r="H14" s="245"/>
-      <c r="I14" s="246"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="247" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="248"/>
-      <c r="C15" s="248"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="248"/>
-      <c r="H15" s="248"/>
-      <c r="I15" s="249"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59" t="s">
+      <c r="B20" s="256"/>
+      <c r="C20" s="256"/>
+      <c r="D20" s="256"/>
+      <c r="E20" s="256"/>
+      <c r="F20" s="256"/>
+      <c r="G20" s="256"/>
+      <c r="H20" s="256"/>
+      <c r="I20" s="257"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="60"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="60"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="208" t="s">
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="60"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="60"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="211" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="209"/>
-      <c r="C18" s="209"/>
-      <c r="D18" s="209"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="209"/>
-      <c r="G18" s="209"/>
-      <c r="H18" s="209"/>
-      <c r="I18" s="210"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="60"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="238" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="239"/>
-      <c r="C21" s="239"/>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="240"/>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="212"/>
+      <c r="E23" s="212"/>
+      <c r="F23" s="212"/>
+      <c r="G23" s="212"/>
+      <c r="H23" s="212"/>
+      <c r="I23" s="213"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="60"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="208" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="209"/>
+      <c r="C26" s="209"/>
+      <c r="D26" s="209"/>
+      <c r="E26" s="209"/>
+      <c r="F26" s="209"/>
+      <c r="G26" s="209"/>
+      <c r="H26" s="209"/>
+      <c r="I26" s="210"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="208"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="209"/>
+      <c r="F27" s="209"/>
+      <c r="G27" s="209"/>
+      <c r="H27" s="209"/>
+      <c r="I27" s="210"/>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="241"/>
+      <c r="B28" s="242"/>
+      <c r="C28" s="242"/>
+      <c r="D28" s="242"/>
+      <c r="E28" s="242"/>
+      <c r="F28" s="242"/>
+      <c r="G28" s="242"/>
+      <c r="H28" s="242"/>
+      <c r="I28" s="243"/>
+    </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A26:I28"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A10:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:I12"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4547,18 +4633,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="253" t="s">
+      <c r="A1" s="267" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="254"/>
-      <c r="C1" s="255"/>
-      <c r="E1" s="253" t="s">
+      <c r="B1" s="268"/>
+      <c r="C1" s="269"/>
+      <c r="E1" s="267" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="254"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="252"/>
-      <c r="I1" s="252"/>
+      <c r="F1" s="268"/>
+      <c r="G1" s="269"/>
+      <c r="H1" s="266"/>
+      <c r="I1" s="266"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4599,10 +4685,10 @@
       <c r="G3" s="12">
         <v>0</v>
       </c>
-      <c r="N3" s="257" t="s">
+      <c r="N3" s="271" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="255" t="s">
+      <c r="O3" s="269" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4626,8 +4712,8 @@
         <v>0</v>
       </c>
       <c r="M4" s="27"/>
-      <c r="N4" s="258"/>
-      <c r="O4" s="256"/>
+      <c r="N4" s="272"/>
+      <c r="O4" s="270"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
